--- a/مسودات_يزيد_فاتورة_فاتورة.xlsx
+++ b/مسودات_يزيد_فاتورة_فاتورة.xlsx
@@ -581,10 +581,10 @@
         <v>293.75</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>5</v>
@@ -645,10 +645,10 @@
         <v>63.3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -709,10 +709,10 @@
         <v>494.05</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -773,17 +773,17 @@
         <v>114.2</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>موقوفة — 3 صنف ناقص</t>
+          <t>موقوفة — 2 صنف ناقص</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>موقوفة — 8 صنف مش موجود 🔴</t>
+          <t>موقوفة — 5 صنف مش موجود 🔴</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -1107,15 +1107,25 @@
       <c r="E11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>900921</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>تب كهرباء فيتنامي/ياباني</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1211,15 +1221,25 @@
       <c r="E14" s="3" t="n">
         <v>18.75</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>900917</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>اسفين حجر بناء</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1239,15 +1259,25 @@
       <c r="E15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>701173</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>بربيش ماء شفاف 3/4×25 متر كريستال</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2578,18 +2608,18 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>مفك 5" عادي</t>
+          <t>مفك عادي</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -4300,12 +4330,12 @@
       <c r="H27" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -4376,12 +4406,12 @@
       <c r="H29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -4604,12 +4634,12 @@
       <c r="H35" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -4707,23 +4737,23 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>500601</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>مفة 3/4 حديد</t>
+          <t>مفة حديد 1" صيني</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -4756,12 +4786,12 @@
       <c r="H39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -5422,7 +5452,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>موقوفة — 4 صنف مش موجود 🔴</t>
+          <t>موقوفة — 2 صنف مش موجود 🔴</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -5859,15 +5889,25 @@
       <c r="E17" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>900921</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>تب كهرباء فيتنامي/ياباني</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -5887,15 +5927,25 @@
       <c r="E18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>100485</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>مفك تست كهرباء 14 سم الماني</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>🟡 أكّد المطابقة</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">

--- a/مسودات_يزيد_فاتورة_فاتورة.xlsx
+++ b/مسودات_يزيد_فاتورة_فاتورة.xlsx
@@ -581,17 +581,17 @@
         <v>293.75</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>موقوفة — 5 صنف ناقص</t>
+          <t>موقوفة — 3 صنف ناقص</t>
         </is>
       </c>
     </row>
@@ -741,17 +741,17 @@
         <v>70.75</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>موقوفة — 2 صنف ناقص</t>
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>جاهزة للترحيل</t>
         </is>
       </c>
     </row>
@@ -773,10 +773,10 @@
         <v>114.2</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>موقوفة — 5 صنف مش موجود 🔴</t>
+          <t>موقوفة — 3 صنف مش موجود 🔴</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -1003,15 +1003,25 @@
       <c r="E8" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>701578</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>درل شحن مع اكسسوارات 21 فولت MEAKIDA</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1381,15 +1391,25 @@
       <c r="E19" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>200351</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>شوال معجونة اسمنتية سافيتو</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -4932,7 +4952,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>موقوفة — 2 صنف مش موجود 🔴</t>
+          <t>جاهزة للترحيل ✅</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -5161,15 +5181,25 @@
       <c r="E11" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>200008</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>تب لاصق ورق 1" كريستال</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -5265,15 +5295,25 @@
       <c r="E14" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>🔴 صنف غير موجود</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>700202</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>باكيت مسمار بولاذ 8 سم</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -5940,12 +5980,12 @@
       <c r="H18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">

--- a/مسودات_يزيد_فاتورة_فاتورة.xlsx
+++ b/مسودات_يزيد_فاتورة_فاتورة.xlsx
@@ -73,12 +73,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADEDA"/>
+        <fgColor rgb="00E6F2EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F2EA"/>
+        <fgColor rgb="00FADEDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -581,17 +581,17 @@
         <v>293.75</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>موقوفة — 3 صنف ناقص</t>
+          <t>جاهزة للترحيل</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       <c r="G5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>موقوفة — 4 صنف ناقص</t>
         </is>
@@ -653,7 +653,7 @@
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>جاهزة للترحيل</t>
         </is>
@@ -685,7 +685,7 @@
       <c r="G7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>موقوفة — 1 صنف ناقص</t>
         </is>
@@ -717,7 +717,7 @@
       <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>جاهزة للترحيل</t>
         </is>
@@ -749,7 +749,7 @@
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>جاهزة للترحيل</t>
         </is>
@@ -781,7 +781,7 @@
       <c r="G10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>موقوفة — 2 صنف ناقص</t>
         </is>
@@ -888,7 +888,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>موقوفة — 3 صنف مش موجود 🔴</t>
+          <t>جاهزة للترحيل ✅</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -1016,12 +1016,12 @@
       <c r="H8" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1092,12 +1092,12 @@
       <c r="H10" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1130,12 +1130,12 @@
       <c r="H11" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1168,12 +1168,12 @@
       <c r="H12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1206,12 +1206,12 @@
       <c r="H13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1244,12 +1244,12 @@
       <c r="H14" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1282,12 +1282,12 @@
       <c r="H15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1307,12 +1307,22 @@
       <c r="E16" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>100620</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>لوح جبسمبورد ابيض</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>🔴 صنف غير موجود</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
@@ -1335,12 +1345,22 @@
       <c r="E17" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>100622</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>زاوية جبسمبورد</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>🔴 صنف غير موجود</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -1363,12 +1383,22 @@
       <c r="E18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>100624</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>اوميغا جبسمبورد</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>🔴 صنف غير موجود</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
@@ -1404,12 +1434,12 @@
       <c r="H19" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1442,12 +1472,12 @@
       <c r="H20" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr"/>
@@ -1630,12 +1660,12 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1668,12 +1698,12 @@
       <c r="H8" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1782,12 +1812,12 @@
       <c r="H11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1820,12 +1850,12 @@
       <c r="H12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1896,12 +1926,12 @@
       <c r="H14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1934,12 +1964,12 @@
       <c r="H15" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1972,12 +2002,12 @@
       <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2010,12 +2040,12 @@
       <c r="H17" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2048,12 +2078,12 @@
       <c r="H18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2086,12 +2116,12 @@
       <c r="H19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -2200,12 +2230,12 @@
       <c r="H22" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -2266,12 +2296,12 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -2294,12 +2324,12 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -2322,12 +2352,12 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -2360,12 +2390,12 @@
       <c r="H27" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr"/>
@@ -2558,12 +2588,12 @@
       <c r="H7" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2596,12 +2626,12 @@
       <c r="H8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -2634,12 +2664,12 @@
       <c r="H9" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2672,12 +2702,12 @@
       <c r="H10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2710,12 +2740,12 @@
       <c r="H11" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr"/>
@@ -2908,12 +2938,12 @@
       <c r="H7" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2984,12 +3014,12 @@
       <c r="H9" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -3022,12 +3052,12 @@
       <c r="H10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -3060,12 +3090,12 @@
       <c r="H11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -3098,12 +3128,12 @@
       <c r="H12" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -3212,12 +3242,12 @@
       <c r="H15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -3240,12 +3270,12 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -3278,12 +3308,12 @@
       <c r="H17" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -3316,12 +3346,12 @@
       <c r="H18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -3354,12 +3384,12 @@
       <c r="H19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -3392,12 +3422,12 @@
       <c r="H20" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr"/>
@@ -3590,12 +3620,12 @@
       <c r="H7" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -3628,12 +3658,12 @@
       <c r="H8" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -3666,12 +3696,12 @@
       <c r="H9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -3704,12 +3734,12 @@
       <c r="H10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -3742,12 +3772,12 @@
       <c r="H11" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -3780,12 +3810,12 @@
       <c r="H12" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -3818,12 +3848,12 @@
       <c r="H13" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -3856,12 +3886,12 @@
       <c r="H14" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -3894,12 +3924,12 @@
       <c r="H15" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -3932,12 +3962,12 @@
       <c r="H16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -3970,12 +4000,12 @@
       <c r="H17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -4008,12 +4038,12 @@
       <c r="H18" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -4046,12 +4076,12 @@
       <c r="H19" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -4084,12 +4114,12 @@
       <c r="H20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -4122,12 +4152,12 @@
       <c r="H21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -4160,12 +4190,12 @@
       <c r="H22" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -4198,12 +4228,12 @@
       <c r="H23" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -4236,12 +4266,12 @@
       <c r="H24" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -4274,12 +4304,12 @@
       <c r="H25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -4312,12 +4342,12 @@
       <c r="H26" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -4350,12 +4380,12 @@
       <c r="H27" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -4388,12 +4418,12 @@
       <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -4426,12 +4456,12 @@
       <c r="H29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -4464,12 +4494,12 @@
       <c r="H30" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -4502,12 +4532,12 @@
       <c r="H31" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -4540,12 +4570,12 @@
       <c r="H32" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -4578,12 +4608,12 @@
       <c r="H33" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -4616,12 +4646,12 @@
       <c r="H34" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -4654,12 +4684,12 @@
       <c r="H35" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -4692,12 +4722,12 @@
       <c r="H36" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -4730,12 +4760,12 @@
       <c r="H37" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -4768,12 +4798,12 @@
       <c r="H38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -4806,12 +4836,12 @@
       <c r="H39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -4844,12 +4874,12 @@
       <c r="H40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr"/>
@@ -5042,12 +5072,12 @@
       <c r="H7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -5080,12 +5110,12 @@
       <c r="H8" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -5156,12 +5186,12 @@
       <c r="H10" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -5194,12 +5224,12 @@
       <c r="H11" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -5232,12 +5262,12 @@
       <c r="H12" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -5270,12 +5300,12 @@
       <c r="H13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -5308,12 +5338,12 @@
       <c r="H14" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -5384,12 +5414,12 @@
       <c r="H16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr"/>
@@ -5610,12 +5640,12 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -5686,12 +5716,12 @@
       <c r="H10" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -5724,12 +5754,12 @@
       <c r="H11" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -5790,12 +5820,12 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>🔴 صنف غير موجود</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -5828,12 +5858,12 @@
       <c r="H14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -5866,12 +5896,12 @@
       <c r="H15" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -5904,12 +5934,12 @@
       <c r="H16" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -5942,12 +5972,12 @@
       <c r="H17" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -5980,12 +6010,12 @@
       <c r="H18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -6018,12 +6048,12 @@
       <c r="H19" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr"/>

--- a/مسودات_يزيد_فاتورة_فاتورة.xlsx
+++ b/مسودات_يزيد_فاتورة_فاتورة.xlsx
@@ -134,8 +134,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,10 +581,10 @@
         <v>293.75</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -741,10 +741,10 @@
         <v>70.75</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -967,23 +967,23 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>700899</t>
+          <t>701817</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>طقم زرفيل كامل مع ايادي</t>
+          <t>طقم زرفيل مع ايادي Zero مع 5 مفتاح كمبيوتر</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1048,18 +1048,18 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>شوال اسمنت ابيض</t>
+          <t>شوال اسمنت ابيض 25 كغم</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1480,22 +1480,22 @@
       <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr"/>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="n">
+      <c r="C21" s="11" t="inlineStr"/>
+      <c r="D21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="n">
         <v>293.75</v>
       </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="12" t="inlineStr"/>
-      <c r="J21" s="12" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1736,12 +1736,12 @@
       <c r="H9" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="J9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1774,12 +1774,12 @@
       <c r="H10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1888,12 +1888,12 @@
       <c r="H13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
+      <c r="J13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2154,12 +2154,12 @@
       <c r="H20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -2192,12 +2192,12 @@
       <c r="H21" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr"/>
+      <c r="J21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -2268,12 +2268,12 @@
       <c r="H23" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr"/>
+      <c r="J23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -2398,22 +2398,22 @@
       <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr"/>
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="12" t="n">
+      <c r="C28" s="11" t="inlineStr"/>
+      <c r="D28" s="11" t="inlineStr"/>
+      <c r="E28" s="11" t="n">
         <v>115</v>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="12" t="inlineStr"/>
+      <c r="F28" s="11" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2748,22 +2748,22 @@
       <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr"/>
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="n">
+      <c r="C12" s="11" t="inlineStr"/>
+      <c r="D12" s="11" t="inlineStr"/>
+      <c r="E12" s="11" t="n">
         <v>63.3</v>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr"/>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="12" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2976,12 +2976,12 @@
       <c r="H8" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -3166,12 +3166,12 @@
       <c r="H13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
+      <c r="J13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -3204,12 +3204,12 @@
       <c r="H14" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -3430,22 +3430,22 @@
       <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr"/>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="n">
+      <c r="C21" s="11" t="inlineStr"/>
+      <c r="D21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="n">
         <v>134</v>
       </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="12" t="inlineStr"/>
-      <c r="J21" s="12" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4882,22 +4882,22 @@
       <c r="J40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr"/>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr"/>
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr"/>
-      <c r="D41" s="12" t="inlineStr"/>
-      <c r="E41" s="12" t="n">
+      <c r="C41" s="11" t="inlineStr"/>
+      <c r="D41" s="11" t="inlineStr"/>
+      <c r="E41" s="11" t="n">
         <v>494.05</v>
       </c>
-      <c r="F41" s="12" t="inlineStr"/>
-      <c r="G41" s="12" t="inlineStr"/>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="12" t="inlineStr"/>
-      <c r="J41" s="12" t="inlineStr"/>
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5148,12 +5148,12 @@
       <c r="H9" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="J9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -5370,18 +5370,18 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>جالون اس بي ار SBR</t>
+          <t>جالون اس بي ار SBR تجاري</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>🟡 أكّد المطابقة</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -5422,22 +5422,22 @@
       <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr"/>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr"/>
+      <c r="E17" s="11" t="n">
         <v>70.75</v>
       </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr"/>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5612,12 +5612,12 @@
       <c r="H7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr"/>
+      <c r="J7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -5678,12 +5678,12 @@
       <c r="H9" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="J9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -5792,12 +5792,12 @@
       <c r="H12" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>🟡 أكّد المطابقة</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
+      <c r="J12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -6037,16 +6037,16 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>701637</t>
+          <t>701642</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>جالون اس بي ار SBR</t>
+          <t>جالون اس بي ار SBR تيراكو</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -6056,22 +6056,22 @@
       <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="n">
+      <c r="C20" s="11" t="inlineStr"/>
+      <c r="D20" s="11" t="inlineStr"/>
+      <c r="E20" s="11" t="n">
         <v>114.2</v>
       </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr"/>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="12" t="inlineStr"/>
-      <c r="J20" s="12" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="11" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
